--- a/data/trans_orig/IP05A05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP05A05-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21259</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36047</t>
+          <t>36525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>34245</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45997</t>
+          <t>45756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65972</t>
+          <t>66013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>53379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69872</t>
+          <t>69894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>42021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58235</t>
+          <t>57709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>100533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122718</t>
+          <t>123261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19388</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>28206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43183</t>
+          <t>42559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29771</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28456</t>
+          <t>28858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42739</t>
+          <t>43096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49130</t>
+          <t>48393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68834</t>
+          <t>68868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44718</t>
+          <t>44861</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60061</t>
+          <t>60310</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33056</t>
+          <t>32893</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47453</t>
+          <t>47056</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>82395</t>
+          <t>82308</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103430</t>
+          <t>102810</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26049</t>
+          <t>25767</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33899</t>
+          <t>33304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37183</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56218</t>
+          <t>54680</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33355</t>
+          <t>33384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46366</t>
+          <t>45894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41698</t>
+          <t>41680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57850</t>
+          <t>57780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78549</t>
+          <t>79993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99245</t>
+          <t>99672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,51%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>29257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39374</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57121</t>
+          <t>57672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78848</t>
+          <t>78769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51208</t>
+          <t>50756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71900</t>
+          <t>70871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113377</t>
+          <t>112857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143901</t>
+          <t>142313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79810</t>
+          <t>79989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102539</t>
+          <t>103553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93812</t>
+          <t>94527</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117138</t>
+          <t>117534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179093</t>
+          <t>180666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>213152</t>
+          <t>213839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52791</t>
+          <t>51469</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28164</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>45314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>66508</t>
+          <t>66162</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91705</t>
+          <t>90713</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>23950</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39522</t>
+          <t>39786</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54897</t>
+          <t>55425</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76166</t>
+          <t>77596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36824</t>
+          <t>37556</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52812</t>
+          <t>52919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54764</t>
+          <t>53918</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72642</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96132</t>
+          <t>95318</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>121044</t>
+          <t>120478</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35253</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22886</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37889</t>
+          <t>37997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47289</t>
+          <t>48048</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67690</t>
+          <t>69213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>30065</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>21763</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>34309</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42085</t>
+          <t>42533</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60669</t>
+          <t>61318</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,64%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32635</t>
+          <t>32655</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>46775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>29773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43214</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65951</t>
+          <t>65485</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85354</t>
+          <t>85291</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27504</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>173992</t>
+          <t>174815</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>211437</t>
+          <t>213715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>192527</t>
+          <t>191984</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>231239</t>
+          <t>230036</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>377793</t>
+          <t>378845</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>430191</t>
+          <t>433514</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>309423</t>
+          <t>310231</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>348668</t>
+          <t>349646</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>323691</t>
+          <t>326007</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>366253</t>
+          <t>366735</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>644792</t>
+          <t>641219</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>704141</t>
+          <t>703254</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99562</t>
+          <t>98263</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>131162</t>
+          <t>129007</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109417</t>
+          <t>111897</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>140587</t>
+          <t>144557</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>216886</t>
+          <t>215654</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>262221</t>
+          <t>262536</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19577</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33514</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>19172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>32852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41118</t>
+          <t>41873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61901</t>
+          <t>61679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34361</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50440</t>
+          <t>50511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33620</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48473</t>
+          <t>48377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72008</t>
+          <t>72180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93742</t>
+          <t>93934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17155</t>
+          <t>17472</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30980</t>
+          <t>30563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55300</t>
+          <t>54809</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31309</t>
+          <t>30959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44440</t>
+          <t>44627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65440</t>
+          <t>63769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38005</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53625</t>
+          <t>53553</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>30781</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47399</t>
+          <t>46777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>73161</t>
+          <t>74687</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95686</t>
+          <t>95038</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30530</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>41440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60432</t>
+          <t>61131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>39070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20834</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34276</t>
+          <t>34551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47918</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68464</t>
+          <t>68554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>28960</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44442</t>
+          <t>43780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47619</t>
+          <t>48053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66462</t>
+          <t>66902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88871</t>
+          <t>87873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26689</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28982</t>
+          <t>29929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>46752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60056</t>
+          <t>59476</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81793</t>
+          <t>82017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54262</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76116</t>
+          <t>76164</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119987</t>
+          <t>119793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150746</t>
+          <t>152134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66108</t>
+          <t>67322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89988</t>
+          <t>89648</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107048</t>
+          <t>106004</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130638</t>
+          <t>131574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180034</t>
+          <t>179271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214586</t>
+          <t>213857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46939</t>
+          <t>46614</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68800</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35069</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54404</t>
+          <t>56480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86750</t>
+          <t>86125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116379</t>
+          <t>115809</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51999</t>
+          <t>51877</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71415</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42481</t>
+          <t>42721</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>61617</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99602</t>
+          <t>99523</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126819</t>
+          <t>126580</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49929</t>
+          <t>49194</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69648</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48899</t>
+          <t>49887</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68801</t>
+          <t>68958</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>104708</t>
+          <t>104934</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>132170</t>
+          <t>133070</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37886</t>
+          <t>37021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>22563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>38521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48523</t>
+          <t>48662</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70576</t>
+          <t>72773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>19171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24858</t>
+          <t>25144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>24838</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>40882</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>18376</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27694</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>41879</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49493</t>
+          <t>48547</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67518</t>
+          <t>67970</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>21674</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14978</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28059</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29117</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45232</t>
+          <t>46053</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>205676</t>
+          <t>207235</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>246107</t>
+          <t>245918</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>198637</t>
+          <t>196611</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>238647</t>
+          <t>236994</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>413900</t>
+          <t>414023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>473076</t>
+          <t>474729</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>266111</t>
+          <t>265295</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>307193</t>
+          <t>308871</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>310803</t>
+          <t>311953</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>354340</t>
+          <t>356087</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>585154</t>
+          <t>589616</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>650526</t>
+          <t>652574</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>145731</t>
+          <t>148627</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>181788</t>
+          <t>185443</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>147915</t>
+          <t>148325</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>186184</t>
+          <t>183743</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>306506</t>
+          <t>306484</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>359396</t>
+          <t>357539</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22294</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>31798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46902</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58184</t>
+          <t>57876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79635</t>
+          <t>78775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30037</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44064</t>
+          <t>44447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28643</t>
+          <t>29027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44834</t>
+          <t>44430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62674</t>
+          <t>63036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83326</t>
+          <t>84315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31569</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32348</t>
+          <t>32117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50568</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>29920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45453</t>
+          <t>46297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>22517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>37630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>58380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79621</t>
+          <t>80149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35631</t>
+          <t>37002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53066</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46501</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63410</t>
+          <t>64235</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>87325</t>
+          <t>86485</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111131</t>
+          <t>111229</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31023</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>20707</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35271</t>
+          <t>35336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41154</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61254</t>
+          <t>61923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33409</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>19090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>32642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42997</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61803</t>
+          <t>61110</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27795</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37409</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43558</t>
+          <t>43237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>62071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24865</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42170</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74174</t>
+          <t>74702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99039</t>
+          <t>98756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69698</t>
+          <t>69297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93058</t>
+          <t>94194</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152410</t>
+          <t>151195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182942</t>
+          <t>183588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78549</t>
+          <t>79019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101572</t>
+          <t>102181</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69629</t>
+          <t>69497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92253</t>
+          <t>92260</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155016</t>
+          <t>154013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>187040</t>
+          <t>187005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>37548</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>56629</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39128</t>
+          <t>38454</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60292</t>
+          <t>59504</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82236</t>
+          <t>81478</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>109538</t>
+          <t>110235</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51948</t>
+          <t>52136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>70026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>55516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>75062</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112768</t>
+          <t>112924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>139183</t>
+          <t>139446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>41026</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58698</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57641</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>85145</t>
+          <t>84944</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110810</t>
+          <t>110922</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35362</t>
+          <t>32904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>38991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44989</t>
+          <t>46356</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67208</t>
+          <t>67280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28186</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27519</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51394</t>
+          <t>49137</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31151</t>
+          <t>31081</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>36426</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46353</t>
+          <t>45453</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63698</t>
+          <t>63085</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>18958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>24484</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>239675</t>
+          <t>242786</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>281798</t>
+          <t>282173</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>240684</t>
+          <t>240833</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>284058</t>
+          <t>282491</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>495396</t>
+          <t>494643</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>550217</t>
+          <t>551494</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>246629</t>
+          <t>247043</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>288554</t>
+          <t>287013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>258890</t>
+          <t>259563</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>301875</t>
+          <t>301775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>519267</t>
+          <t>518245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>578993</t>
+          <t>576587</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>125943</t>
+          <t>123462</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>159596</t>
+          <t>158425</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>149573</t>
+          <t>147834</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>187474</t>
+          <t>185400</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>283233</t>
+          <t>283394</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>334841</t>
+          <t>334870</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72054</t>
+          <t>72593</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86850</t>
+          <t>86297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90223</t>
+          <t>89384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111855</t>
+          <t>110714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168703</t>
+          <t>166619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193538</t>
+          <t>192579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30706</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46613</t>
+          <t>47246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>33953</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67629</t>
+          <t>67808</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>80672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64401</t>
+          <t>64443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79983</t>
+          <t>79061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136332</t>
+          <t>135810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156728</t>
+          <t>156335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>25320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39360</t>
+          <t>40273</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>41833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49831</t>
+          <t>49693</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48557</t>
+          <t>49073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58927</t>
+          <t>58896</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94199</t>
+          <t>94618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106993</t>
+          <t>106927</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>93099</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168558</t>
+          <t>170327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163392</t>
+          <t>164798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>185344</t>
+          <t>186160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246733</t>
+          <t>256655</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>346408</t>
+          <t>347992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30537</t>
+          <t>29677</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109750</t>
+          <t>108233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17337</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33688</t>
+          <t>33931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52447</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>156398</t>
+          <t>155936</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26083</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26742</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23070</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46465</t>
+          <t>45712</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76867</t>
+          <t>76402</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96034</t>
+          <t>95278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112685</t>
+          <t>112864</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134517</t>
+          <t>134597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196330</t>
+          <t>196555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>224377</t>
+          <t>225413</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31730</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18952</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>37962</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36839</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>61971</t>
+          <t>62049</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>32727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53028</t>
+          <t>53268</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63373</t>
+          <t>63111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>52598</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64577</t>
+          <t>64532</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>110703</t>
+          <t>110269</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>126137</t>
+          <t>125200</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>15804</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>414959</t>
+          <t>421468</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>519848</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>566442</t>
+          <t>566663</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>610138</t>
+          <t>609001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1005023</t>
+          <t>989829</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1116425</t>
+          <t>1116861</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,52%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>85187</t>
+          <t>84775</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>205759</t>
+          <t>193271</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>82493</t>
+          <t>83114</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>117771</t>
+          <t>118332</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>178994</t>
+          <t>178771</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>304445</t>
+          <t>316164</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>39220</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65716</t>
+          <t>65026</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>75300</t>
+          <t>74811</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93857</t>
+          <t>93492</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>130785</t>
+          <t>131843</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
